--- a/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-EX-InsuranceProvider.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-EX-InsuranceProvider.xlsx
@@ -1314,7 +1314,7 @@
         <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>106</v>

--- a/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-EX-InsuranceProvider.xlsx
+++ b/tiflow-core/fhir-error-codes/1.0.0-draft/StructureDefinition-GEM-ERP-EX-InsuranceProvider.xlsx
@@ -1314,7 +1314,7 @@
         <v>84</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>106</v>
